--- a/grupos/3ARHM - Estadisticos 20231.xlsx
+++ b/grupos/3ARHM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="109">
   <si>
     <t>Materia</t>
   </si>
@@ -224,24 +224,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -254,70 +254,91 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>MACHORRO</t>
   </si>
   <si>
-    <t>BAEZ</t>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>CHIMALHUA</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>LUIS FELIPE</t>
   </si>
   <si>
     <t>FATIMA</t>
   </si>
   <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
     <t>JIMENA</t>
   </si>
   <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
   </si>
   <si>
     <t>SALMA AISHA</t>
   </si>
   <si>
-    <t>ROSA</t>
+    <t>DANIEL ELEAZAR</t>
   </si>
   <si>
     <t>ALEXANDRA</t>
@@ -834,19 +855,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -873,13 +894,13 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -911,19 +932,19 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -950,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -959,7 +980,7 @@
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -988,19 +1009,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1027,7 +1048,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1065,19 +1086,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1107,7 +1128,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1142,19 +1163,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1178,10 +1199,10 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1219,19 +1240,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1296,19 +1317,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1332,13 +1353,13 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1373,19 +1394,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1412,13 +1433,13 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1450,19 +1471,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1492,7 +1513,7 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1527,19 +1548,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1575,7 +1596,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1604,19 +1625,19 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1643,13 +1664,13 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1681,19 +1702,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1717,19 +1738,19 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1758,19 +1779,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1794,7 +1815,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1806,7 +1827,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1835,19 +1856,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1883,7 +1904,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1912,19 +1933,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1960,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1989,19 +2010,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2025,7 +2046,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2034,7 +2055,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2066,19 +2087,19 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2105,16 +2126,16 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>5</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2143,19 +2164,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2182,7 +2203,7 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2191,7 +2212,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2220,19 +2241,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2256,16 +2277,16 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>10</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2297,19 +2318,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2333,7 +2354,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2342,7 +2363,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2374,19 +2395,19 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2410,19 +2431,19 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2451,19 +2472,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2490,16 +2511,16 @@
         <v>9</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2528,19 +2549,19 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2605,19 +2626,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2644,7 +2665,7 @@
         <v>9</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2682,19 +2703,19 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2718,10 +2739,10 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2730,7 +2751,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2759,19 +2780,19 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2795,19 +2816,19 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>5</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2836,19 +2857,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2872,16 +2893,16 @@
         <v>5</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>5</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -2913,19 +2934,19 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2984,19 +3005,19 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3023,10 +3044,10 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3055,19 +3076,19 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3091,16 +3112,16 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3120,13 +3141,13 @@
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3141,10 +3162,10 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3173,19 +3194,19 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3215,10 +3236,10 @@
         <v>7</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>9</v>
@@ -3250,19 +3271,19 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3292,7 +3313,7 @@
         <v>8</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3327,19 +3348,19 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3363,7 +3384,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -3372,7 +3393,7 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y37">
         <v>8</v>
@@ -3404,19 +3425,19 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3443,7 +3464,7 @@
         <v>9</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3481,19 +3502,19 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3517,19 +3538,19 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V39">
         <v>6</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3558,19 +3579,19 @@
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3600,7 +3621,7 @@
         <v>8</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3635,19 +3656,19 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3671,16 +3692,16 @@
         <v>8</v>
       </c>
       <c r="U41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V41">
         <v>6</v>
       </c>
       <c r="W41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y41">
         <v>5</v>
@@ -3712,19 +3733,19 @@
         <v>-1</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -3754,7 +3775,7 @@
         <v>9</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X42">
         <v>10</v>
@@ -3789,19 +3810,19 @@
         <v>-1</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -3828,7 +3849,7 @@
         <v>9</v>
       </c>
       <c r="V43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W43">
         <v>5</v>
@@ -3837,7 +3858,7 @@
         <v>9</v>
       </c>
       <c r="Y43">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3866,19 +3887,19 @@
         <v>-1</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -3902,16 +3923,16 @@
         <v>10</v>
       </c>
       <c r="U44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y44">
         <v>8</v>
@@ -3943,19 +3964,19 @@
         <v>-1</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -3982,10 +4003,10 @@
         <v>8</v>
       </c>
       <c r="V45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X45">
         <v>8</v>
@@ -4020,19 +4041,19 @@
         <v>-1</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4056,16 +4077,16 @@
         <v>10</v>
       </c>
       <c r="U46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V46">
         <v>8</v>
       </c>
       <c r="W46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y46">
         <v>10</v>
@@ -4097,19 +4118,19 @@
         <v>-1</v>
       </c>
       <c r="I47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N47">
         <v>-1</v>
@@ -4133,10 +4154,10 @@
         <v>7</v>
       </c>
       <c r="U47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W47">
         <v>5</v>
@@ -4284,7 +4305,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -4296,13 +4317,13 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -4314,7 +4335,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4355,7 +4376,7 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N5">
         <v>100</v>
@@ -4373,7 +4394,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4402,7 +4423,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -4414,13 +4435,13 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -4432,7 +4453,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4461,7 +4482,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -4473,13 +4494,13 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -4491,7 +4512,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4579,7 +4600,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -4597,7 +4618,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -4638,7 +4659,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -4650,13 +4671,13 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -4668,7 +4689,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4756,7 +4777,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4774,7 +4795,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -4815,10 +4836,10 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -4833,10 +4854,10 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4886,7 +4907,7 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N14">
         <v>100</v>
@@ -4904,7 +4925,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4936,7 +4957,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -4954,7 +4975,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4992,7 +5013,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -5004,13 +5025,13 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -5022,7 +5043,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -5110,37 +5131,37 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J18">
+        <v>97.5</v>
+      </c>
+      <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18">
         <v>95</v>
       </c>
-      <c r="K18">
-        <v>100</v>
-      </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>90</v>
-      </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P18">
+        <v>97.5</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
+        <v>100</v>
+      </c>
+      <c r="S18">
         <v>95</v>
-      </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
-        <v>100</v>
-      </c>
-      <c r="S18">
-        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -5169,7 +5190,7 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -5181,13 +5202,13 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -5199,7 +5220,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -5290,17 +5311,17 @@
         <v>100</v>
       </c>
       <c r="J21">
+        <v>95</v>
+      </c>
+      <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
+        <v>100</v>
+      </c>
+      <c r="M21">
         <v>90</v>
       </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
-      <c r="M21">
-        <v>100</v>
-      </c>
       <c r="N21">
         <v>100</v>
       </c>
@@ -5308,16 +5329,16 @@
         <v>100</v>
       </c>
       <c r="P21">
+        <v>95</v>
+      </c>
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
         <v>90</v>
-      </c>
-      <c r="Q21">
-        <v>100</v>
-      </c>
-      <c r="R21">
-        <v>100</v>
-      </c>
-      <c r="S21">
-        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -5358,7 +5379,7 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -5376,7 +5397,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5405,10 +5426,10 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -5417,16 +5438,16 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N23">
         <v>100</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5435,7 +5456,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5464,7 +5485,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -5476,13 +5497,13 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N24">
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5494,7 +5515,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5585,7 +5606,7 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -5594,7 +5615,7 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -5603,7 +5624,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5612,7 +5633,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5641,7 +5662,7 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -5659,7 +5680,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -5700,7 +5721,7 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J28">
         <v>100</v>
@@ -5718,7 +5739,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -5759,37 +5780,37 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J29">
         <v>90</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M29">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="N29">
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P29">
         <v>90</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="S29">
-        <v>90</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5818,7 +5839,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5830,13 +5851,13 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N30">
         <v>100</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -5848,7 +5869,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5877,10 +5898,10 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -5889,16 +5910,16 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N31">
         <v>100</v>
       </c>
       <c r="O31">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5907,7 +5928,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5930,34 +5951,34 @@
         <v>90</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J32">
+        <v>97.5</v>
+      </c>
+      <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
         <v>95</v>
       </c>
-      <c r="K32">
-        <v>100</v>
-      </c>
-      <c r="L32">
-        <v>90</v>
-      </c>
       <c r="M32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P32">
+        <v>97.5</v>
+      </c>
+      <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
         <v>95</v>
       </c>
-      <c r="Q32">
-        <v>100</v>
-      </c>
-      <c r="R32">
-        <v>90</v>
-      </c>
       <c r="S32">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5986,7 +6007,7 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5995,7 +6016,7 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M33">
         <v>90</v>
@@ -6004,7 +6025,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -6013,7 +6034,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S33">
         <v>90</v>
@@ -6033,22 +6054,22 @@
         <v>90</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J34">
+        <v>97.5</v>
+      </c>
+      <c r="L34">
         <v>95</v>
       </c>
-      <c r="L34">
-        <v>90</v>
-      </c>
       <c r="O34">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P34">
+        <v>97.5</v>
+      </c>
+      <c r="R34">
         <v>95</v>
-      </c>
-      <c r="R34">
-        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -6089,7 +6110,7 @@
         <v>100</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N35">
         <v>100</v>
@@ -6107,7 +6128,7 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -6207,7 +6228,7 @@
         <v>100</v>
       </c>
       <c r="M37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N37">
         <v>100</v>
@@ -6225,7 +6246,7 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6313,10 +6334,10 @@
         <v>100</v>
       </c>
       <c r="I39">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="J39">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K39">
         <v>100</v>
@@ -6331,10 +6352,10 @@
         <v>100</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="P39">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q39">
         <v>100</v>
@@ -6431,7 +6452,7 @@
         <v>100</v>
       </c>
       <c r="I41">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J41">
         <v>100</v>
@@ -6449,7 +6470,7 @@
         <v>100</v>
       </c>
       <c r="O41">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P41">
         <v>100</v>
@@ -6502,7 +6523,7 @@
         <v>100</v>
       </c>
       <c r="M42">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N42">
         <v>100</v>
@@ -6520,7 +6541,7 @@
         <v>100</v>
       </c>
       <c r="S42">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6738,7 +6759,7 @@
         <v>100</v>
       </c>
       <c r="M46">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N46">
         <v>100</v>
@@ -6756,7 +6777,7 @@
         <v>100</v>
       </c>
       <c r="S46">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -6785,10 +6806,10 @@
         <v>100</v>
       </c>
       <c r="I47">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J47">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K47">
         <v>100</v>
@@ -6803,10 +6824,10 @@
         <v>100</v>
       </c>
       <c r="O47">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P47">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q47">
         <v>100</v>
@@ -6872,7 +6893,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
@@ -6893,7 +6914,7 @@
         <v>30.2</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6904,7 +6925,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
@@ -6913,16 +6934,16 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>72.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>27.9</v>
+        <v>18.6</v>
       </c>
       <c r="H3">
         <v>7.4</v>
@@ -6945,19 +6966,19 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
       <c r="G4" s="2">
-        <v>20.5</v>
+        <v>18.2</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7000,7 +7021,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>72</v>
@@ -7009,16 +7030,16 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
       <c r="G6" s="2">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="H6">
         <v>8.5</v>
@@ -7032,7 +7053,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
@@ -7053,7 +7074,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7103,7 +7124,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7135,22 +7156,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920054</v>
+        <v>22330051920333</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7158,19 +7179,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920054</v>
+        <v>22330051920333</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>68</v>
@@ -7181,22 +7202,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920068</v>
+        <v>22330051920053</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7204,19 +7225,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920068</v>
+        <v>22330051920053</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>68</v>
@@ -7227,22 +7248,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920053</v>
+        <v>22330051920054</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7250,22 +7271,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920059</v>
+        <v>22330051920054</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7276,19 +7297,19 @@
         <v>22330051920061</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7296,22 +7317,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920062</v>
+        <v>22330051920061</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
         <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7319,22 +7340,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920070</v>
+        <v>22330051920068</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
         <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7342,19 +7363,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920081</v>
+        <v>22330051920068</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>69</v>
@@ -7365,24 +7386,185 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
+        <v>21330051920053</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920053</v>
+      </c>
+      <c r="B13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920084</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920084</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920062</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920064</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920081</v>
+      </c>
+      <c r="B18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
         <v>22330051920079</v>
       </c>
-      <c r="B12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12">
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHM - Estadisticos 20231.xlsx
+++ b/grupos/3ARHM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="112">
   <si>
     <t>Materia</t>
   </si>
@@ -254,27 +254,30 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>AYOHUA</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -284,24 +287,27 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>COXCAHUA</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>CHIMALHUA</t>
   </si>
   <si>
@@ -314,25 +320,28 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
     <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
   </si>
   <si>
     <t>SALMA AISHA</t>
@@ -852,7 +861,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>9</v>
@@ -888,7 +897,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -929,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>8</v>
@@ -965,7 +974,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -1006,7 +1015,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -1083,7 +1092,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>8</v>
@@ -1119,7 +1128,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1160,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>8</v>
@@ -1237,7 +1246,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -1314,7 +1323,7 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>8</v>
@@ -1350,7 +1359,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1391,7 +1400,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>9</v>
@@ -1468,7 +1477,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>9</v>
@@ -1504,7 +1513,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1545,7 +1554,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -1622,7 +1631,7 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -1699,7 +1708,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>9</v>
@@ -1735,7 +1744,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1776,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -1812,7 +1821,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -1853,7 +1862,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -1930,7 +1939,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -1966,7 +1975,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -2007,7 +2016,7 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>9</v>
@@ -2084,7 +2093,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>8</v>
@@ -2161,7 +2170,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>9</v>
@@ -2197,7 +2206,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2238,7 +2247,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>9</v>
@@ -2274,7 +2283,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2315,7 +2324,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -2392,7 +2401,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>8</v>
@@ -2469,7 +2478,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -2505,7 +2514,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>9</v>
@@ -2546,7 +2555,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>6</v>
@@ -2582,7 +2591,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -2623,7 +2632,7 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -2700,7 +2709,7 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
         <v>8</v>
@@ -2777,7 +2786,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I29">
         <v>5</v>
@@ -2813,7 +2822,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -2854,7 +2863,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>8</v>
@@ -2931,7 +2940,7 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>7</v>
@@ -2967,7 +2976,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>8</v>
@@ -3073,7 +3082,7 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
         <v>6</v>
@@ -3109,7 +3118,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3191,7 +3200,7 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>9</v>
@@ -3268,7 +3277,7 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
         <v>9</v>
@@ -3345,7 +3354,7 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
         <v>9</v>
@@ -3381,7 +3390,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>9</v>
@@ -3422,7 +3431,7 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
         <v>9</v>
@@ -3499,7 +3508,7 @@
         <v>7</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I39">
         <v>8</v>
@@ -3576,7 +3585,7 @@
         <v>9</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
         <v>9</v>
@@ -3612,7 +3621,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U40">
         <v>10</v>
@@ -3653,7 +3662,7 @@
         <v>5</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I41">
         <v>5</v>
@@ -3730,7 +3739,7 @@
         <v>10</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I42">
         <v>10</v>
@@ -3807,7 +3816,7 @@
         <v>7</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I43">
         <v>9</v>
@@ -3843,7 +3852,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U43">
         <v>9</v>
@@ -3884,7 +3893,7 @@
         <v>8</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I44">
         <v>7</v>
@@ -3961,7 +3970,7 @@
         <v>7</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I45">
         <v>7</v>
@@ -4038,7 +4047,7 @@
         <v>10</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I46">
         <v>10</v>
@@ -4115,7 +4124,7 @@
         <v>5</v>
       </c>
       <c r="H47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I47">
         <v>7</v>
@@ -4151,7 +4160,7 @@
         <v>-1</v>
       </c>
       <c r="T47">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U47">
         <v>6</v>
@@ -4597,7 +4606,7 @@
         <v>90</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I9">
         <v>97</v>
@@ -4615,7 +4624,7 @@
         <v>90</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O9">
         <v>97</v>
@@ -5128,7 +5137,7 @@
         <v>90</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I18">
         <v>93.90000000000001</v>
@@ -5146,7 +5155,7 @@
         <v>95</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O18">
         <v>93.90000000000001</v>
@@ -5777,7 +5786,7 @@
         <v>90</v>
       </c>
       <c r="H29">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I29">
         <v>90.90000000000001</v>
@@ -5795,7 +5804,7 @@
         <v>50</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O29">
         <v>90.90000000000001</v>
@@ -6998,19 +7007,19 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>92.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7124,7 +7133,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7156,22 +7165,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920333</v>
+        <v>22330051920053</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7179,16 +7188,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920333</v>
+        <v>22330051920053</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7202,16 +7211,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920053</v>
+        <v>22330051920054</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -7225,22 +7234,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920053</v>
+        <v>22330051920054</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7248,16 +7257,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920054</v>
+        <v>22330051920061</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -7271,22 +7280,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920054</v>
+        <v>22330051920061</v>
       </c>
       <c r="B7" t="s">
         <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7294,16 +7303,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920061</v>
+        <v>22330051920212</v>
       </c>
       <c r="B8" t="s">
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -7317,16 +7326,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920061</v>
+        <v>22330051920212</v>
       </c>
       <c r="B9" t="s">
         <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -7346,10 +7355,10 @@
         <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -7369,10 +7378,10 @@
         <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -7392,10 +7401,10 @@
         <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -7415,10 +7424,10 @@
         <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -7438,10 +7447,10 @@
         <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -7461,10 +7470,10 @@
         <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -7478,16 +7487,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920062</v>
+        <v>22330051920333</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -7501,16 +7510,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920064</v>
+        <v>22330051920062</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -7524,16 +7533,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920081</v>
+        <v>22330051920064</v>
       </c>
       <c r="B18" t="s">
         <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -7547,24 +7556,47 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920079</v>
+        <v>22330051920081</v>
       </c>
       <c r="B19" t="s">
         <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920079</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
         <v>69</v>
       </c>
-      <c r="G19">
+      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHM - Estadisticos 20231.xlsx
+++ b/grupos/3ARHM - Estadisticos 20231.xlsx
@@ -4606,7 +4606,7 @@
         <v>90</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I9">
         <v>97</v>
@@ -4624,7 +4624,7 @@
         <v>90</v>
       </c>
       <c r="N9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O9">
         <v>97</v>
@@ -5137,7 +5137,7 @@
         <v>90</v>
       </c>
       <c r="H18">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>93.90000000000001</v>
@@ -5155,7 +5155,7 @@
         <v>95</v>
       </c>
       <c r="N18">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O18">
         <v>93.90000000000001</v>

--- a/grupos/3ARHM - Estadisticos 20231.xlsx
+++ b/grupos/3ARHM - Estadisticos 20231.xlsx
@@ -1785,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -1821,7 +1821,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>7</v>

--- a/grupos/3ARHM - Estadisticos 20231.xlsx
+++ b/grupos/3ARHM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -254,106 +254,67 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AYOHUA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
   </si>
   <si>
     <t>DANIELA</t>
   </si>
   <si>
-    <t>CLAUDIA PAOLA</t>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>JIMENA</t>
   </si>
   <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>SALMA AISHA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>ALEXANDRA</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
+    <t>JESUS ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -879,34 +840,34 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>9</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -956,28 +917,28 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>7</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -1033,40 +994,40 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1110,34 +1071,34 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>10</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1187,22 +1148,22 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1217,7 +1178,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1264,22 +1225,22 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1291,7 +1252,7 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1341,22 +1302,22 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1365,16 +1326,16 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1418,22 +1379,22 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1442,7 +1403,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1495,22 +1456,22 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1522,13 +1483,13 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1572,28 +1533,28 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>9</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1605,7 +1566,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1649,22 +1610,22 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1676,7 +1637,7 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1726,34 +1687,34 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>10</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>5</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1803,22 +1764,22 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1827,16 +1788,16 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1880,22 +1841,22 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1957,28 +1918,28 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>6</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -1990,7 +1951,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2034,22 +1995,22 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2058,7 +2019,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2111,34 +2072,34 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2188,22 +2149,22 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2221,7 +2182,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2265,22 +2226,22 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2289,7 +2250,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2342,22 +2303,22 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>6</v>
@@ -2369,13 +2330,13 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2419,22 +2380,22 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2449,10 +2410,10 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2496,22 +2457,22 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2523,13 +2484,13 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2573,28 +2534,28 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -2606,7 +2567,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2650,22 +2611,22 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2674,13 +2635,13 @@
         <v>9</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2727,28 +2688,28 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>10</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2760,7 +2721,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2804,31 +2765,31 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -2881,22 +2842,22 @@
         <v>1</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>5</v>
@@ -2958,28 +2919,28 @@
         <v>3</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>9</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>5</v>
@@ -3029,22 +2990,22 @@
         <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3053,10 +3014,10 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3100,31 +3061,31 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>8</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3133,7 +3094,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3159,19 +3120,19 @@
         <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>7</v>
@@ -3218,22 +3179,22 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3245,7 +3206,7 @@
         <v>7</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3295,22 +3256,22 @@
         <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3372,31 +3333,31 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>10</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3405,7 +3366,7 @@
         <v>10</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3449,22 +3410,22 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3526,22 +3487,22 @@
         <v>8</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3559,7 +3520,7 @@
         <v>10</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3603,34 +3564,34 @@
         <v>9</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>10</v>
       </c>
       <c r="V40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3680,34 +3641,34 @@
         <v>5</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T41">
         <v>8</v>
       </c>
       <c r="U41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V41">
         <v>6</v>
       </c>
       <c r="W41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X41">
         <v>8</v>
@@ -3757,22 +3718,22 @@
         <v>10</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>10</v>
@@ -3781,10 +3742,10 @@
         <v>10</v>
       </c>
       <c r="V42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X42">
         <v>10</v>
@@ -3834,22 +3795,22 @@
         <v>9</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T43">
         <v>9</v>
@@ -3861,13 +3822,13 @@
         <v>6</v>
       </c>
       <c r="W43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>9</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3911,22 +3872,22 @@
         <v>7</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T44">
         <v>10</v>
@@ -3935,10 +3896,10 @@
         <v>8</v>
       </c>
       <c r="V44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X44">
         <v>9</v>
@@ -3988,22 +3949,22 @@
         <v>6</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T45">
         <v>10</v>
@@ -4012,7 +3973,7 @@
         <v>8</v>
       </c>
       <c r="V45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W45">
         <v>8</v>
@@ -4065,22 +4026,22 @@
         <v>9</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T46">
         <v>10</v>
@@ -4089,7 +4050,7 @@
         <v>10</v>
       </c>
       <c r="V46">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W46">
         <v>9</v>
@@ -4142,37 +4103,37 @@
         <v>5</v>
       </c>
       <c r="N47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T47">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U47">
         <v>6</v>
       </c>
       <c r="V47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W47">
         <v>5</v>
       </c>
       <c r="X47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y47">
         <v>5</v>
@@ -4332,7 +4293,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>98.5</v>
+        <v>98.2</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -4344,7 +4305,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4391,7 +4352,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -4403,7 +4364,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4450,7 +4411,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>97</v>
+        <v>98.2</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -4462,7 +4423,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4509,7 +4470,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>98.5</v>
+        <v>98.2</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -4521,7 +4482,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>95</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4627,7 +4588,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>97</v>
+        <v>97.3</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -4639,7 +4600,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4686,7 +4647,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>90.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -4698,7 +4659,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4804,7 +4765,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>98.5</v>
+        <v>98.2</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -4863,10 +4824,10 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>97</v>
+        <v>98.2</v>
       </c>
       <c r="P13">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4875,7 +4836,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4934,7 +4895,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4984,7 +4945,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -5040,7 +5001,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>92.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -5052,7 +5013,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -5158,19 +5119,19 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>93.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="P18">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="S18">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -5217,7 +5178,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>98.5</v>
+        <v>98.2</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -5229,7 +5190,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -5288,7 +5249,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -5335,10 +5296,10 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P21">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -5347,7 +5308,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -5394,7 +5355,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -5406,7 +5367,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5453,10 +5414,10 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>97</v>
+        <v>97.3</v>
       </c>
       <c r="P23">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5465,7 +5426,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>95</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5512,7 +5473,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>97</v>
+        <v>98.2</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5524,7 +5485,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5633,7 +5594,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5642,7 +5603,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5689,7 +5650,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>98.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -5748,7 +5709,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -5760,7 +5721,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5804,22 +5765,22 @@
         <v>50</v>
       </c>
       <c r="N29">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="O29">
-        <v>90.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="P29">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="Q29">
-        <v>68.8</v>
+        <v>45.8</v>
       </c>
       <c r="R29">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="S29">
-        <v>50</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5866,10 +5827,10 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>92.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="P30">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5878,7 +5839,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>90</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5925,10 +5886,10 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>90.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="P31">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5937,7 +5898,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>70</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5975,19 +5936,19 @@
         <v>95</v>
       </c>
       <c r="O32">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P32">
-        <v>97.5</v>
+        <v>90</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="R32">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S32">
-        <v>95</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -6034,7 +5995,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>92.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -6043,10 +6004,10 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S33">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -6072,13 +6033,13 @@
         <v>95</v>
       </c>
       <c r="O34">
-        <v>90.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="P34">
-        <v>97.5</v>
+        <v>90</v>
       </c>
       <c r="R34">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -6137,7 +6098,7 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -6243,7 +6204,7 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -6255,7 +6216,7 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6361,10 +6322,10 @@
         <v>100</v>
       </c>
       <c r="O39">
-        <v>98.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="P39">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q39">
         <v>100</v>
@@ -6373,7 +6334,7 @@
         <v>100</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -6479,7 +6440,7 @@
         <v>100</v>
       </c>
       <c r="O41">
-        <v>90.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="P41">
         <v>100</v>
@@ -6491,7 +6452,7 @@
         <v>100</v>
       </c>
       <c r="S41">
-        <v>90</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -6550,7 +6511,7 @@
         <v>100</v>
       </c>
       <c r="S42">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6597,7 +6558,7 @@
         <v>100</v>
       </c>
       <c r="O43">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P43">
         <v>100</v>
@@ -6609,7 +6570,7 @@
         <v>100</v>
       </c>
       <c r="S43">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -6786,7 +6747,7 @@
         <v>100</v>
       </c>
       <c r="S46">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -6833,10 +6794,10 @@
         <v>100</v>
       </c>
       <c r="O47">
-        <v>95.5</v>
+        <v>97.3</v>
       </c>
       <c r="P47">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q47">
         <v>100</v>
@@ -6845,7 +6806,7 @@
         <v>100</v>
       </c>
       <c r="S47">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6911,16 +6872,16 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2">
-        <v>69.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>30.2</v>
+        <v>20.9</v>
       </c>
       <c r="H2">
         <v>7.2</v>
@@ -6943,19 +6904,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
-        <v>81.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>18.6</v>
+        <v>20.9</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6987,7 +6948,7 @@
         <v>18.2</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7007,19 +6968,19 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="G5" s="2">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7051,7 +7012,7 @@
         <v>2.3</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7083,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7133,7 +7094,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7165,22 +7126,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920053</v>
+        <v>22330051920079</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7188,22 +7149,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920053</v>
+        <v>22330051920079</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7211,22 +7172,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920054</v>
+        <v>22330051920084</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7234,16 +7195,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920054</v>
+        <v>22330051920084</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -7257,22 +7218,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920061</v>
+        <v>22330051920333</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7283,19 +7244,19 @@
         <v>22330051920061</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7303,16 +7264,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920212</v>
+        <v>22330051920334</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -7326,16 +7287,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920212</v>
+        <v>22330051920068</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -7349,254 +7310,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920068</v>
+        <v>22330051920317</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920068</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920053</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920053</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920084</v>
-      </c>
-      <c r="B14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920084</v>
-      </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920333</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920062</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920064</v>
-      </c>
-      <c r="B18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920081</v>
-      </c>
-      <c r="B19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920079</v>
-      </c>
-      <c r="B20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHM - Estadisticos 20231.xlsx
+++ b/grupos/3ARHM - Estadisticos 20231.xlsx
@@ -858,22 +858,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -935,22 +935,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>5</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1012,22 +1012,22 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1092,7 +1092,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1101,7 +1101,7 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1169,19 +1169,19 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1246,19 +1246,19 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1320,22 +1320,22 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1400,19 +1400,19 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1477,19 +1477,19 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1551,22 +1551,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1634,10 +1634,10 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1708,19 +1708,19 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>5</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1782,22 +1782,22 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1874,7 +1874,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1936,10 +1936,10 @@
         <v>5</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -1948,7 +1948,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2016,19 +2016,19 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2090,22 +2090,22 @@
         <v>7</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2170,19 +2170,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2244,22 +2244,22 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>10</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2321,22 +2321,22 @@
         <v>8</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2401,19 +2401,19 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2475,22 +2475,22 @@
         <v>10</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2552,22 +2552,22 @@
         <v>7</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>5</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2629,22 +2629,22 @@
         <v>10</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2709,19 +2709,19 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2786,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -2863,16 +2863,16 @@
         <v>5</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>5</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -2937,10 +2937,10 @@
         <v>8</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>5</v>
@@ -2949,7 +2949,7 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3005,7 +3005,7 @@
         <v>4</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3014,7 +3014,7 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>5</v>
@@ -3079,19 +3079,19 @@
         <v>5</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3129,13 +3129,13 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3203,16 +3203,16 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3280,10 +3280,10 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3354,10 +3354,10 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3366,7 +3366,7 @@
         <v>10</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3431,10 +3431,10 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3508,19 +3508,19 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>10</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3582,22 +3582,22 @@
         <v>10</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U40">
         <v>10</v>
       </c>
       <c r="V40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X40">
         <v>10</v>
       </c>
       <c r="Y40">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3659,19 +3659,19 @@
         <v>6</v>
       </c>
       <c r="T41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W41">
         <v>5</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y41">
         <v>5</v>
@@ -3742,10 +3742,10 @@
         <v>10</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X42">
         <v>10</v>
@@ -3813,22 +3813,22 @@
         <v>10</v>
       </c>
       <c r="T43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V43">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y43">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3893,19 +3893,19 @@
         <v>10</v>
       </c>
       <c r="U44">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V44">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W44">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y44">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -3970,19 +3970,19 @@
         <v>10</v>
       </c>
       <c r="U45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V45">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y45">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -4050,13 +4050,13 @@
         <v>10</v>
       </c>
       <c r="V46">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y46">
         <v>10</v>
@@ -4121,19 +4121,19 @@
         <v>5</v>
       </c>
       <c r="T47">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U47">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V47">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W47">
         <v>5</v>
       </c>
       <c r="X47">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y47">
         <v>5</v>
@@ -6884,7 +6884,7 @@
         <v>20.9</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6916,7 +6916,7 @@
         <v>20.9</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6948,7 +6948,7 @@
         <v>18.2</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6980,7 +6980,7 @@
         <v>4.8</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7012,7 +7012,7 @@
         <v>2.3</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7044,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3ARHM - Estadisticos 20231.xlsx
+++ b/grupos/3ARHM - Estadisticos 20231.xlsx
@@ -858,22 +858,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -935,22 +935,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>5</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1012,22 +1012,22 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1092,7 +1092,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1101,7 +1101,7 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1169,19 +1169,19 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1246,19 +1246,19 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1320,22 +1320,22 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1400,19 +1400,19 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1477,19 +1477,19 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1551,22 +1551,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1634,10 +1634,10 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1708,19 +1708,19 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>5</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1782,22 +1782,22 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1874,7 +1874,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1936,10 +1936,10 @@
         <v>5</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -1948,7 +1948,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2016,19 +2016,19 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2090,22 +2090,22 @@
         <v>7</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2170,19 +2170,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2244,22 +2244,22 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>10</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2321,22 +2321,22 @@
         <v>8</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2401,19 +2401,19 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2475,22 +2475,22 @@
         <v>10</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2552,22 +2552,22 @@
         <v>7</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>5</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2629,22 +2629,22 @@
         <v>10</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2709,19 +2709,19 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2786,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -2863,16 +2863,16 @@
         <v>5</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>5</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -2937,10 +2937,10 @@
         <v>8</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>5</v>
@@ -2949,7 +2949,7 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3005,7 +3005,7 @@
         <v>4</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3014,7 +3014,7 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>5</v>
@@ -3079,19 +3079,19 @@
         <v>5</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3129,13 +3129,13 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3203,16 +3203,16 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3280,10 +3280,10 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3354,10 +3354,10 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3366,7 +3366,7 @@
         <v>10</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3431,10 +3431,10 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3508,19 +3508,19 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>10</v>
       </c>
       <c r="Y39">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3582,22 +3582,22 @@
         <v>10</v>
       </c>
       <c r="T40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>10</v>
       </c>
       <c r="V40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>10</v>
       </c>
       <c r="Y40">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3659,19 +3659,19 @@
         <v>6</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W41">
         <v>5</v>
       </c>
       <c r="X41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y41">
         <v>5</v>
@@ -3742,10 +3742,10 @@
         <v>10</v>
       </c>
       <c r="V42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X42">
         <v>10</v>
@@ -3813,22 +3813,22 @@
         <v>10</v>
       </c>
       <c r="T43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V43">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y43">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3893,19 +3893,19 @@
         <v>10</v>
       </c>
       <c r="U44">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V44">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W44">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y44">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -3970,19 +3970,19 @@
         <v>10</v>
       </c>
       <c r="U45">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V45">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W45">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X45">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y45">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -4050,13 +4050,13 @@
         <v>10</v>
       </c>
       <c r="V46">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y46">
         <v>10</v>
@@ -4121,19 +4121,19 @@
         <v>5</v>
       </c>
       <c r="T47">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U47">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V47">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W47">
         <v>5</v>
       </c>
       <c r="X47">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y47">
         <v>5</v>
@@ -6884,7 +6884,7 @@
         <v>20.9</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6916,7 +6916,7 @@
         <v>20.9</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6948,7 +6948,7 @@
         <v>18.2</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6980,7 +6980,7 @@
         <v>4.8</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7012,7 +7012,7 @@
         <v>2.3</v>
       </c>
       <c r="H6">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7044,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
